--- a/submission/COMAVI_v7.12_SI/S2_Table.xlsx
+++ b/submission/COMAVI_v7.12_SI/S2_Table.xlsx
@@ -58,8 +58,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -426,26 +427,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Supporting information item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>sheet</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>source item in the reviewed manuscript</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>caption</t>
         </is>
@@ -454,153 +461,198 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>S2 Table</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>operating_point_sweep</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>S7 Table</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>S7 Table. Complete operating-point sweep. MC is weighted mechanism consistency; balanced MC gives structural and benchmark-negative classes equal weight.</t>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>S2 Table, operating_point_sweep sheet. Complete operating-point sweep. MC is weighted mechanism consistency; balanced MC gives structural and benchmark-negative classes equal weight. (S7 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>S2 Table</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>disagreement_classes</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>S8 Table</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>S8 Table. Disagreement classes at the 2.5 kcal/mol operating point, excluding the barnase Glu73 cluster.</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>S2 Table, disagreement_classes sheet. Disagreement classes at the 2.5 kcal/mol operating point, excluding the barnase Glu73 cluster. (S8 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>S2 Table</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>tier_distribution</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>S9 Table</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>S9 Table. Structural-mechanism distribution by tier.</t>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>S2 Table, tier_distribution sheet. Structural-mechanism distribution by tier. (S9 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>S2 Table</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>evidence_states</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>S10 Table</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>S10 Table. Four evidence states across thresholds. Each cell is structural mechanism / no-lesion variant.</t>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>S2 Table, evidence_states sheet. Four evidence states across thresholds. Each cell is structural mechanism / no-lesion variant. (S10 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>S2 Table</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>detection_metrics</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>S11 Table</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>S11 Table. Structural-mechanism detection metrics. Values are sensitivity / specificity / positive predictive value.</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>S2 Table, detection_metrics sheet. Structural-mechanism detection metrics. Values are sensitivity / specificity / positive predictive value. (S11 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>S2 Table</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>pathogenicity_ranking</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>S12 Table</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>S12 Table. Descriptive pathogenicity ranking on the common complete-case population.</t>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>S2 Table, pathogenicity_ranking sheet. Descriptive pathogenicity ranking on the common complete-case population. (S12 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>S2 Table</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>robustness</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>S13 Table</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>S13 Table. Mechanism-pattern and four-output robustness analyses at the 2.5 kcal/mol reference.</t>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>S2 Table, robustness sheet. Mechanism-pattern and four-output robustness analyses at the 2.5 kcal/mol reference. (S13 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>S2 Table</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>skempi_validation</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>S14 Table</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>S14 Table. Independent binding-axis validation.</t>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>S2 Table, skempi_validation sheet. Independent binding-axis validation. (S14 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>S2 Table</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>threshold_sweep</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>S15 Table</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S15 Table. Every graded metric at every decision threshold, including post hoc points. The five rows above the rule are the prespecified set, unchanged since the repository's first commit and fixed before the graded ground truth existed in committed form; the three below it were evaluated after the </t>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>S2 Table, threshold_sweep sheet. Every graded metric at every decision threshold, including post hoc points. The five rows above the rule are the prespecified set, unchanged since the repository's first commit and fixed before the graded ground truth existed in committed form; the three below it were evaluated after the (S15 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
@@ -615,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -630,197 +682,110 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Threshold (kcal/mol)</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Detection</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Attribution</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Correct rejection</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Whole-variant score</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Axis: isolated subunit</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Axis: in complex</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Axis: binding</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Structural agreement</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0.920</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0.760</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.156</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.579</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.720</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.545</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.800</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.710</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>S2 Table, threshold_sweep sheet. Every graded metric at every decision threshold, including post hoc points. The five rows above the rule are the prespecified set, unchanged since the repository's first commit and fixed before the graded ground truth existed in committed form; the three below it were evaluated after the (S15 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>Threshold (kcal/mol)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>Detection</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.680</t>
+          <t>Attribution</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>Correct rejection</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>Whole-variant score</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.680</t>
+          <t>Axis: isolated subunit</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>Axis: in complex</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>Axis: binding</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>Structural agreement</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>0.920</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.760</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.156</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.579</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.720</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.545</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>0.800</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.640</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.719</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.684</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0.760</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.727</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.767</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>0.710</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2.5 (reference)</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -830,69 +795,69 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.560</t>
+          <t>0.680</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>0.594</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>0.649</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.760</t>
+          <t>0.680</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>0.727</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>0.734</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2.9/2.9/3.5</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.720</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.480</t>
+          <t>0.640</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>0.719</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.711</t>
+          <t>0.684</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.720</t>
+          <t>0.760</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -902,76 +867,76 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>0.767</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>0.742</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3.0 (post hoc)</t>
+          <t>2.5 (reference)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.640</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.560</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>0.812</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.719</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.680</t>
+          <t>0.760</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>0.773</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.700</t>
+          <t>0.733</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.702</t>
+          <t>0.742</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3.5 (post hoc)</t>
+          <t>2.9/2.9/3.5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.520</t>
+          <t>0.720</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.360</t>
+          <t>0.480</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -981,17 +946,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.711</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.640</t>
+          <t>0.720</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>0.727</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1001,52 +966,146 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.702</t>
+          <t>0.726</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>3.0 (post hoc)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.640</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.400</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.844</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.680</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.682</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.700</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.702</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3.5 (post hoc)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.520</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.360</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.844</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.640</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.682</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.733</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.702</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>4.0 (post hoc)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>0.480</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>0.280</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>0.938</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>0.600</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>0.727</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>0.700</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>0.694</t>
         </is>
@@ -1063,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1075,192 +1134,199 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Operating point</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Structural arm (n = 25)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Rejection arm (n = 32)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Pooled score (n = 57)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Balanced score</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Measured destabilizations called (n = 44)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1.0 default</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0.760</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0.438</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.579</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.599</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>35/44</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>S2 Table, operating_point_sweep sheet. Complete operating-point sweep. MC is weighted mechanism consistency; balanced MC gives structural and benchmark-negative classes equal weight. (S7 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>Operating point</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.720</t>
+          <t>Structural arm (n = 25)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>Rejection arm (n = 32)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>Pooled score (n = 57)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.657</t>
+          <t>Balanced score</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26/44</t>
+          <t>Measured destabilizations called (n = 44)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0 default</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.640</t>
+          <t>0.760</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>0.438</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.684</t>
+          <t>0.579</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.679</t>
+          <t>0.599</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19/44</t>
+          <t>35/44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2.5 reference</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.720</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>0.594</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>0.649</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>0.657</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>13/44</t>
+          <t>26/44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.640</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.719</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.684</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.679</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>19/44</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2.5 reference</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.812</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.719</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.706</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>13/44</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>tSAP</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>0.540</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0.844</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>0.711</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>0.692</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>12/44</t>
         </is>
@@ -1277,119 +1343,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Call relationship</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Median absolute error</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Benchmark examples</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Agreement</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Measured and predicted calls agree.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.67 kcal/mol</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Most comparisons</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>S2 Table, disagreement_classes sheet. Disagreement classes at the 2.5 kcal/mol operating point, excluding the barnase Glu73 cluster. (S8 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Borderline disagreement</t>
+          <t>Call relationship</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>n</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Calls straddle 2.5 kcal/mol but both values sit near it.</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.79 kcal/mol</t>
+          <t>Median absolute error</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>V1665M</t>
+          <t>Benchmark examples</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Agreement</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Measured and predicted calls agree.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.67 kcal/mol</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Most comparisons</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Borderline disagreement</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Calls straddle 2.5 kcal/mol but both values sit near it.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.79 kcal/mol</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>V1665M</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Substantive disagreement</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Calls straddle 2.5 kcal/mol and at least one value is far from it.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>2.96 kcal/mol</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>V1736A; V1808A</t>
         </is>
@@ -1406,7 +1479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1416,88 +1489,95 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tier group</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Structural mechanism</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Benchmark negative</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Structural fraction</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Tier 1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>11/13 = 0.846</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>S2 Table, tier_distribution sheet. Structural-mechanism distribution by tier. (S9 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier group</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Structural mechanism</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>Benchmark negative</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6/17 = 0.353</t>
+          <t>Structural fraction</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>11/13 = 0.846</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6/17 = 0.353</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Tiers 3-4</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>0/17 = 0.000</t>
         </is>
@@ -1514,7 +1594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1525,162 +1605,169 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Operating point</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Convergent</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Energy-only</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Context-only</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Neither</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1.0 default</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>16/9</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0/8</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1/4</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0/9</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>S2 Table, evidence_states sheet. Four evidence states across thresholds. Each cell is structural mechanism / no-lesion variant. (S10 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>Operating point</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15/6</t>
+          <t>Convergent</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>Energy-only</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2/7</t>
+          <t>Context-only</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0/11</t>
+          <t>Neither</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0 default</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15/4</t>
+          <t>16/9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>0/8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0/12</t>
+          <t>0/9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2.5 reference</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15/3</t>
+          <t>15/6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0/14</t>
+          <t>0/11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>15/4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2.5 reference</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15/3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>tSAP</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>11/3</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0/2</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>6/10</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>0/15</t>
         </is>
@@ -1697,7 +1784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1706,102 +1793,109 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Operating point</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Any energetic firing</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Convergent: energy + Tier 1-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1.0 default</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0.941 / 0.433 / 0.485</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0.941 / 0.700 / 0.640</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>S2 Table, detection_metrics sheet. Structural-mechanism detection metrics. Values are sensitivity / specificity / positive predictive value. (S11 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>Operating point</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.882 / 0.600 / 0.556</t>
+          <t>Any energetic firing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.882 / 0.800 / 0.714</t>
+          <t>Convergent: energy + Tier 1-2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0 default</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.882 / 0.700 / 0.625</t>
+          <t>0.941 / 0.433 / 0.485</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.882 / 0.867 / 0.789</t>
+          <t>0.941 / 0.700 / 0.640</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2.5 reference</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>0.882 / 0.600 / 0.556</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>0.882 / 0.800 / 0.714</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.882 / 0.900 / 0.833</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.882 / 0.700 / 0.625</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.882 / 0.867 / 0.789</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2.5 reference</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.882 / 0.800 / 0.714</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.882 / 0.900 / 0.833</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>tSAP</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>0.647 / 0.833 / 0.688</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0.647 / 0.900 / 0.786</t>
         </is>
@@ -1818,7 +1912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1827,85 +1921,92 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Descriptor</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Pathogenicity AUC</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Intended interpretation</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AlphaMissense</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0.903</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Pathogenicity ranking</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>S2 Table, pathogenicity_ranking sheet. Descriptive pathogenicity ranking on the common complete-case population. (S12 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ISDS-v1</t>
+          <t>Descriptor</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>Pathogenicity AUC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Integrated structural-disruption priority</t>
+          <t>Intended interpretation</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ISDS energetic component</t>
+          <t>AlphaMissense</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>0.903</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Energetic structural evidence</t>
+          <t>Pathogenicity ranking</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>ISDS-v1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.851</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Integrated structural-disruption priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ISDS energetic component</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.836</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Energetic structural evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>ISDS context component</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>0.769</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Structural-context strength</t>
         </is>
@@ -1922,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1931,119 +2032,126 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Weighted mechanism consistency</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Four-output continuity aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Observed at 2.5</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0.719</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0.742</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>S2 Table, robustness sheet. Mechanism-pattern and four-output robustness analyses at the 2.5 kcal/mol reference. (S13 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Block-permutation null, n = 2,000</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.484 ± 0.052; p = 5 × 10^-4</t>
+          <t>Weighted mechanism consistency</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.535 ± 0.046; p = 5 × 10^-4</t>
+          <t>Four-output continuity aggregate</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Leave one system out</t>
+          <t>Observed at 2.5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.7037-0.7500</t>
+          <t>0.719</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.7265-0.7589</t>
+          <t>0.742</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Replicate noise, n = 500</t>
+          <t>Block-permutation null, n = 2,000</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.721 ± 0.013</t>
+          <t>0.484 ± 0.052; p = 5 × 10^-4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.740 ± 0.004</t>
+          <t>0.535 ± 0.046; p = 5 × 10^-4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Variant bootstrap, n = 2,000</t>
+          <t>Leave one system out</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>95% CI 0.614-0.819</t>
+          <t>0.7037-0.7500</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>95% CI 0.664-0.820</t>
+          <t>0.7265-0.7589</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Replicate noise, n = 500</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.721 ± 0.013</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.740 ± 0.004</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Variant bootstrap, n = 2,000</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>95% CI 0.614-0.819</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>95% CI 0.664-0.820</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>System-cluster bootstrap, n = 2,000</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>95% CI 0.625-0.821</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>95% CI 0.682-0.816</t>
         </is>
@@ -2060,11 +2168,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -2072,110 +2180,53 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Methods</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Pearson r</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Spearman ρ</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Sign-correct on destabilizers</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Barnase-barstar, all</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ITC 10; stopped-flow 9; inactivation 5</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.37 (p = 0.074)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.30 (p = 0.156)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>14/22 (64%)</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>S2 Table, skempi_validation sheet. Independent binding-axis validation. (S14 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Barnase-barstar, excluding Glu73</t>
+          <t>Complex</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>stopped-flow 9; inactivation 5; ITC 3</t>
+          <t>Methods</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>n</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.51 (p = 0.035)</t>
+          <t>Pearson r</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.56 (p = 0.019)</t>
+          <t>Spearman ρ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14/15 (93%)</t>
+          <t>Sign-correct on destabilizers</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TEM1-BLIP, BLIP side</t>
+          <t>Barnase-barstar, all</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ITC 17; stopped-flow 5; SPR 1; inactivation 1</t>
+          <t>ITC 10; stopped-flow 9; inactivation 5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2185,47 +2236,111 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.51 (p = 0.010)</t>
+          <t>0.37 (p = 0.074)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.50 (p = 0.012)</t>
+          <t>0.30 (p = 0.156)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16/18 (89%)</t>
+          <t>14/22 (64%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Barnase-barstar, excluding Glu73</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>stopped-flow 9; inactivation 5; ITC 3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.51 (p = 0.035)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.56 (p = 0.019)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>14/15 (93%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TEM1-BLIP, BLIP side</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ITC 17; stopped-flow 5; SPR 1; inactivation 1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.51 (p = 0.010)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.50 (p = 0.012)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>16/18 (89%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Combined, excluding Glu73 cluster</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>0.48 (p = 0.002)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>0.55 (p = 0.0002)</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>30/33 (91%)</t>
         </is>

--- a/submission/COMAVI_v7.12_SI/S2_Table.xlsx
+++ b/submission/COMAVI_v7.12_SI/S2_Table.xlsx
@@ -688,6 +688,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1140,6 +1141,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1303,7 +1305,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tSAP</t>
+          <t>Substitution-adjusted</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1360,6 +1362,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1495,6 +1498,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1611,6 +1615,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1749,7 +1754,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tSAP</t>
+          <t>Substitution-adjusted</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1799,6 +1804,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1887,7 +1893,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tSAP</t>
+          <t>Substitution-adjusted</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1927,6 +1933,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2038,6 +2045,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2186,6 +2194,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
